--- a/output/2026-09-01_04_Italia_Umbria_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-01_04_Italia_Umbria_Impiantistica_aspirazione_industriale.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Indirizzo: Via dei Loggi 51, 06135 Ponte San Giovanni (PG). Verificata su fonte ufficiale simar.it e directory sihappy.it. Deduplicati i siti satellite impiantidiaspirazioneariaterni.it e impiantifiltrazionefumiepolveriterni.it, confermati appartenere alla stessa azienda.</t>
+          <t>Indirizzo: Via dei Loggi 51, 06135 Ponte San Giovanni (PG). Verificata su fonte ufficiale simar.it e directory sihappy.it. Deduplicati i siti satellite impiantidiaspirazioneariaterni.it e impiantifiltrazionefumiepolveriterni.it, confermati appartenere alla stessa azienda. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Indirizzo: Via dei Carrozzieri 2, 05014 Castel Viscardo (TR). Fondata 1985, operativa su Umbria/Toscana/Lazio/Sicilia. Confermata su PagineGialle, PagineBianche, Virgilio, reteimprese.it e sito ufficiale.</t>
+          <t>Indirizzo: Via dei Carrozzieri 2, 05014 Castel Viscardo (TR). Fondata 1985, operativa su Umbria/Toscana/Lazio/Sicilia. Confermata su PagineGialle, PagineBianche, Virgilio, reteimprese.it e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-01_03_Italia_Umbria_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
